--- a/academias/Electricidad - Estadisticos 20211.xlsx
+++ b/academias/Electricidad - Estadisticos 20211.xlsx
@@ -513,25 +513,25 @@
         <v>32</v>
       </c>
       <c r="E2">
-        <v>25</v>
+        <v>32</v>
       </c>
       <c r="F2">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="G2">
-        <v>78.13</v>
+        <v>100</v>
       </c>
       <c r="H2">
-        <v>21.88</v>
+        <v>0</v>
       </c>
       <c r="I2">
-        <v>9.6</v>
+        <v>9.1</v>
       </c>
       <c r="J2">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="K2">
-        <v>21.88</v>
+        <v>0</v>
       </c>
     </row>
     <row r="3" spans="1:11">
@@ -548,25 +548,25 @@
         <v>38</v>
       </c>
       <c r="E3">
-        <v>27</v>
+        <v>38</v>
       </c>
       <c r="F3">
-        <v>11</v>
+        <v>0</v>
       </c>
       <c r="G3">
-        <v>71.05</v>
+        <v>100</v>
       </c>
       <c r="H3">
-        <v>28.95</v>
+        <v>0</v>
       </c>
       <c r="I3">
-        <v>9.800000000000001</v>
+        <v>9.1</v>
       </c>
       <c r="J3">
-        <v>11</v>
+        <v>0</v>
       </c>
       <c r="K3">
-        <v>28.95</v>
+        <v>0</v>
       </c>
     </row>
     <row r="4" spans="1:11">
@@ -583,25 +583,25 @@
         <v>38</v>
       </c>
       <c r="E4">
-        <v>28</v>
+        <v>38</v>
       </c>
       <c r="F4">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="G4">
-        <v>73.68000000000001</v>
+        <v>100</v>
       </c>
       <c r="H4">
-        <v>26.32</v>
+        <v>0</v>
       </c>
       <c r="I4">
-        <v>9.800000000000001</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="J4">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="K4">
-        <v>26.32</v>
+        <v>0</v>
       </c>
     </row>
     <row r="5" spans="1:11">
@@ -618,25 +618,25 @@
         <v>32</v>
       </c>
       <c r="E5">
-        <v>23</v>
+        <v>32</v>
       </c>
       <c r="F5">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="G5">
-        <v>71.88</v>
+        <v>100</v>
       </c>
       <c r="H5">
-        <v>28.13</v>
+        <v>0</v>
       </c>
       <c r="I5">
-        <v>9.699999999999999</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="J5">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="K5">
-        <v>28.13</v>
+        <v>0</v>
       </c>
     </row>
     <row r="6" spans="1:11">
@@ -653,25 +653,25 @@
         <v>32</v>
       </c>
       <c r="E6">
-        <v>22</v>
+        <v>32</v>
       </c>
       <c r="F6">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="G6">
-        <v>68.75</v>
+        <v>100</v>
       </c>
       <c r="H6">
-        <v>31.25</v>
+        <v>0</v>
       </c>
       <c r="I6">
-        <v>9.699999999999999</v>
+        <v>9</v>
       </c>
       <c r="J6">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="K6">
-        <v>31.25</v>
+        <v>0</v>
       </c>
     </row>
     <row r="7" spans="1:11">
@@ -758,25 +758,25 @@
         <v>32</v>
       </c>
       <c r="E9">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="F9">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="G9">
-        <v>81.25</v>
+        <v>87.5</v>
       </c>
       <c r="H9">
-        <v>18.75</v>
+        <v>12.5</v>
       </c>
       <c r="I9">
-        <v>8.199999999999999</v>
+        <v>7.7</v>
       </c>
       <c r="J9">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="K9">
-        <v>18.75</v>
+        <v>0</v>
       </c>
     </row>
     <row r="10" spans="1:11">
@@ -793,25 +793,25 @@
         <v>38</v>
       </c>
       <c r="E10">
-        <v>26</v>
+        <v>32</v>
       </c>
       <c r="F10">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="G10">
-        <v>68.42</v>
+        <v>84.20999999999999</v>
       </c>
       <c r="H10">
-        <v>31.58</v>
+        <v>15.79</v>
       </c>
       <c r="I10">
-        <v>8.699999999999999</v>
+        <v>7.8</v>
       </c>
       <c r="J10">
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="K10">
-        <v>31.58</v>
+        <v>0</v>
       </c>
     </row>
     <row r="11" spans="1:11">
@@ -828,25 +828,25 @@
         <v>32</v>
       </c>
       <c r="E11">
-        <v>22</v>
+        <v>25</v>
       </c>
       <c r="F11">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="G11">
-        <v>68.75</v>
+        <v>78.13</v>
       </c>
       <c r="H11">
-        <v>31.25</v>
+        <v>21.88</v>
       </c>
       <c r="I11">
-        <v>8</v>
+        <v>7.1</v>
       </c>
       <c r="J11">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="K11">
-        <v>31.25</v>
+        <v>0</v>
       </c>
     </row>
     <row r="12" spans="1:11">
@@ -968,25 +968,25 @@
         <v>33</v>
       </c>
       <c r="E15">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="F15">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="G15">
-        <v>57.58</v>
+        <v>66.67</v>
       </c>
       <c r="H15">
-        <v>42.42</v>
+        <v>33.33</v>
       </c>
       <c r="I15">
-        <v>8.300000000000001</v>
+        <v>7.2</v>
       </c>
       <c r="J15">
-        <v>14</v>
+        <v>0</v>
       </c>
       <c r="K15">
-        <v>42.42</v>
+        <v>0</v>
       </c>
     </row>
     <row r="16" spans="1:11">
@@ -1003,25 +1003,25 @@
         <v>23</v>
       </c>
       <c r="E16">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="F16">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="G16">
-        <v>69.56999999999999</v>
+        <v>82.61</v>
       </c>
       <c r="H16">
-        <v>30.43</v>
+        <v>17.39</v>
       </c>
       <c r="I16">
-        <v>8</v>
+        <v>7.4</v>
       </c>
       <c r="J16">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="K16">
-        <v>30.43</v>
+        <v>0</v>
       </c>
     </row>
   </sheetData>
@@ -1087,22 +1087,25 @@
         <v>32</v>
       </c>
       <c r="E2">
-        <v>0</v>
+        <v>32</v>
       </c>
       <c r="F2">
-        <v>32</v>
+        <v>0</v>
       </c>
       <c r="G2">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="H2">
-        <v>100</v>
+        <v>0</v>
+      </c>
+      <c r="I2">
+        <v>9.1</v>
       </c>
       <c r="J2">
-        <v>32</v>
+        <v>0</v>
       </c>
       <c r="K2">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="3" spans="1:11">
@@ -1119,22 +1122,25 @@
         <v>38</v>
       </c>
       <c r="E3">
-        <v>0</v>
+        <v>38</v>
       </c>
       <c r="F3">
-        <v>38</v>
+        <v>0</v>
       </c>
       <c r="G3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="H3">
-        <v>100</v>
+        <v>0</v>
+      </c>
+      <c r="I3">
+        <v>9.1</v>
       </c>
       <c r="J3">
-        <v>38</v>
+        <v>0</v>
       </c>
       <c r="K3">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="4" spans="1:11">
@@ -1151,22 +1157,25 @@
         <v>38</v>
       </c>
       <c r="E4">
-        <v>0</v>
+        <v>38</v>
       </c>
       <c r="F4">
-        <v>38</v>
+        <v>0</v>
       </c>
       <c r="G4">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="H4">
-        <v>100</v>
+        <v>0</v>
+      </c>
+      <c r="I4">
+        <v>9.199999999999999</v>
       </c>
       <c r="J4">
-        <v>38</v>
+        <v>0</v>
       </c>
       <c r="K4">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="5" spans="1:11">
@@ -1183,22 +1192,25 @@
         <v>32</v>
       </c>
       <c r="E5">
-        <v>0</v>
+        <v>32</v>
       </c>
       <c r="F5">
-        <v>32</v>
+        <v>0</v>
       </c>
       <c r="G5">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="H5">
-        <v>100</v>
+        <v>0</v>
+      </c>
+      <c r="I5">
+        <v>9</v>
       </c>
       <c r="J5">
-        <v>32</v>
+        <v>0</v>
       </c>
       <c r="K5">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="6" spans="1:11">
@@ -1215,22 +1227,25 @@
         <v>32</v>
       </c>
       <c r="E6">
-        <v>0</v>
+        <v>32</v>
       </c>
       <c r="F6">
-        <v>32</v>
+        <v>0</v>
       </c>
       <c r="G6">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="H6">
-        <v>100</v>
+        <v>0</v>
+      </c>
+      <c r="I6">
+        <v>9</v>
       </c>
       <c r="J6">
-        <v>32</v>
+        <v>0</v>
       </c>
       <c r="K6">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="7" spans="1:11">
@@ -1311,22 +1326,25 @@
         <v>32</v>
       </c>
       <c r="E9">
-        <v>0</v>
+        <v>27</v>
       </c>
       <c r="F9">
-        <v>32</v>
+        <v>5</v>
       </c>
       <c r="G9">
-        <v>0</v>
+        <v>84.38</v>
       </c>
       <c r="H9">
-        <v>100</v>
+        <v>15.63</v>
+      </c>
+      <c r="I9">
+        <v>7.5</v>
       </c>
       <c r="J9">
-        <v>32</v>
+        <v>0</v>
       </c>
       <c r="K9">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="10" spans="1:11">
@@ -1343,22 +1361,25 @@
         <v>38</v>
       </c>
       <c r="E10">
-        <v>0</v>
+        <v>31</v>
       </c>
       <c r="F10">
-        <v>38</v>
+        <v>7</v>
       </c>
       <c r="G10">
-        <v>0</v>
+        <v>81.58</v>
       </c>
       <c r="H10">
-        <v>100</v>
+        <v>18.42</v>
+      </c>
+      <c r="I10">
+        <v>7.5</v>
       </c>
       <c r="J10">
-        <v>38</v>
+        <v>0</v>
       </c>
       <c r="K10">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="11" spans="1:11">
@@ -1375,22 +1396,25 @@
         <v>32</v>
       </c>
       <c r="E11">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="F11">
-        <v>32</v>
+        <v>7</v>
       </c>
       <c r="G11">
-        <v>0</v>
+        <v>78.13</v>
       </c>
       <c r="H11">
-        <v>100</v>
+        <v>21.88</v>
+      </c>
+      <c r="I11">
+        <v>6.8</v>
       </c>
       <c r="J11">
-        <v>32</v>
+        <v>0</v>
       </c>
       <c r="K11">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="12" spans="1:11">
@@ -1503,22 +1527,25 @@
         <v>33</v>
       </c>
       <c r="E15">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="F15">
-        <v>33</v>
+        <v>21</v>
       </c>
       <c r="G15">
-        <v>0</v>
+        <v>36.36</v>
       </c>
       <c r="H15">
-        <v>100</v>
+        <v>63.64</v>
+      </c>
+      <c r="I15">
+        <v>9</v>
       </c>
       <c r="J15">
-        <v>33</v>
+        <v>21</v>
       </c>
       <c r="K15">
-        <v>100</v>
+        <v>63.64</v>
       </c>
     </row>
     <row r="16" spans="1:11">
@@ -1535,22 +1562,25 @@
         <v>23</v>
       </c>
       <c r="E16">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="F16">
-        <v>23</v>
+        <v>11</v>
       </c>
       <c r="G16">
-        <v>0</v>
+        <v>52.17</v>
       </c>
       <c r="H16">
-        <v>100</v>
+        <v>47.83</v>
+      </c>
+      <c r="I16">
+        <v>9.300000000000001</v>
       </c>
       <c r="J16">
-        <v>23</v>
+        <v>11</v>
       </c>
       <c r="K16">
-        <v>100</v>
+        <v>47.83</v>
       </c>
     </row>
   </sheetData>
@@ -1616,25 +1646,25 @@
         <v>32</v>
       </c>
       <c r="E2">
-        <v>25</v>
+        <v>32</v>
       </c>
       <c r="F2">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="G2">
-        <v>78.13</v>
+        <v>100</v>
       </c>
       <c r="H2">
-        <v>21.88</v>
+        <v>0</v>
       </c>
       <c r="I2">
-        <v>9.6</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="J2">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="K2">
-        <v>21.88</v>
+        <v>0</v>
       </c>
     </row>
     <row r="3" spans="1:11">
@@ -1651,25 +1681,25 @@
         <v>38</v>
       </c>
       <c r="E3">
-        <v>27</v>
+        <v>38</v>
       </c>
       <c r="F3">
-        <v>11</v>
+        <v>0</v>
       </c>
       <c r="G3">
-        <v>71.05</v>
+        <v>100</v>
       </c>
       <c r="H3">
-        <v>28.95</v>
+        <v>0</v>
       </c>
       <c r="I3">
-        <v>9.800000000000001</v>
+        <v>9.1</v>
       </c>
       <c r="J3">
-        <v>11</v>
+        <v>0</v>
       </c>
       <c r="K3">
-        <v>28.95</v>
+        <v>0</v>
       </c>
     </row>
     <row r="4" spans="1:11">
@@ -1686,25 +1716,25 @@
         <v>38</v>
       </c>
       <c r="E4">
-        <v>28</v>
+        <v>38</v>
       </c>
       <c r="F4">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="G4">
-        <v>73.68000000000001</v>
+        <v>100</v>
       </c>
       <c r="H4">
-        <v>26.32</v>
+        <v>0</v>
       </c>
       <c r="I4">
-        <v>9.800000000000001</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="J4">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="K4">
-        <v>26.32</v>
+        <v>0</v>
       </c>
     </row>
     <row r="5" spans="1:11">
@@ -1721,25 +1751,25 @@
         <v>32</v>
       </c>
       <c r="E5">
-        <v>23</v>
+        <v>32</v>
       </c>
       <c r="F5">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="G5">
-        <v>71.88</v>
+        <v>100</v>
       </c>
       <c r="H5">
-        <v>28.13</v>
+        <v>0</v>
       </c>
       <c r="I5">
-        <v>9.699999999999999</v>
+        <v>9.1</v>
       </c>
       <c r="J5">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="K5">
-        <v>28.13</v>
+        <v>0</v>
       </c>
     </row>
     <row r="6" spans="1:11">
@@ -1756,25 +1786,25 @@
         <v>32</v>
       </c>
       <c r="E6">
-        <v>22</v>
+        <v>32</v>
       </c>
       <c r="F6">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="G6">
-        <v>68.75</v>
+        <v>100</v>
       </c>
       <c r="H6">
-        <v>31.25</v>
+        <v>0</v>
       </c>
       <c r="I6">
-        <v>9.699999999999999</v>
+        <v>9</v>
       </c>
       <c r="J6">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="K6">
-        <v>31.25</v>
+        <v>0</v>
       </c>
     </row>
     <row r="7" spans="1:11">
@@ -1861,25 +1891,25 @@
         <v>32</v>
       </c>
       <c r="E9">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="F9">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="G9">
-        <v>81.25</v>
+        <v>84.38</v>
       </c>
       <c r="H9">
-        <v>18.75</v>
+        <v>15.63</v>
       </c>
       <c r="I9">
-        <v>8.199999999999999</v>
+        <v>7.7</v>
       </c>
       <c r="J9">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="K9">
-        <v>18.75</v>
+        <v>0</v>
       </c>
     </row>
     <row r="10" spans="1:11">
@@ -1896,25 +1926,25 @@
         <v>38</v>
       </c>
       <c r="E10">
-        <v>26</v>
+        <v>31</v>
       </c>
       <c r="F10">
-        <v>12</v>
+        <v>7</v>
       </c>
       <c r="G10">
-        <v>68.42</v>
+        <v>81.58</v>
       </c>
       <c r="H10">
-        <v>31.58</v>
+        <v>18.42</v>
       </c>
       <c r="I10">
-        <v>8.699999999999999</v>
+        <v>7.7</v>
       </c>
       <c r="J10">
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="K10">
-        <v>31.58</v>
+        <v>0</v>
       </c>
     </row>
     <row r="11" spans="1:11">
@@ -1931,25 +1961,25 @@
         <v>32</v>
       </c>
       <c r="E11">
-        <v>22</v>
+        <v>25</v>
       </c>
       <c r="F11">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="G11">
-        <v>68.75</v>
+        <v>78.13</v>
       </c>
       <c r="H11">
-        <v>31.25</v>
+        <v>21.88</v>
       </c>
       <c r="I11">
-        <v>8</v>
+        <v>7.1</v>
       </c>
       <c r="J11">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="K11">
-        <v>31.25</v>
+        <v>0</v>
       </c>
     </row>
     <row r="12" spans="1:11">
@@ -2071,25 +2101,25 @@
         <v>33</v>
       </c>
       <c r="E15">
-        <v>19</v>
+        <v>24</v>
       </c>
       <c r="F15">
-        <v>14</v>
+        <v>9</v>
       </c>
       <c r="G15">
-        <v>57.58</v>
+        <v>72.73</v>
       </c>
       <c r="H15">
-        <v>42.42</v>
+        <v>27.27</v>
       </c>
       <c r="I15">
-        <v>8.300000000000001</v>
+        <v>7.5</v>
       </c>
       <c r="J15">
-        <v>14</v>
+        <v>0</v>
       </c>
       <c r="K15">
-        <v>42.42</v>
+        <v>0</v>
       </c>
     </row>
     <row r="16" spans="1:11">
@@ -2106,25 +2136,25 @@
         <v>23</v>
       </c>
       <c r="E16">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="F16">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="G16">
-        <v>69.56999999999999</v>
+        <v>82.61</v>
       </c>
       <c r="H16">
-        <v>30.43</v>
+        <v>17.39</v>
       </c>
       <c r="I16">
-        <v>8</v>
+        <v>7.8</v>
       </c>
       <c r="J16">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="K16">
-        <v>30.43</v>
+        <v>0</v>
       </c>
     </row>
   </sheetData>

--- a/academias/Electricidad - Estadisticos 20211.xlsx
+++ b/academias/Electricidad - Estadisticos 20211.xlsx
@@ -9,7 +9,7 @@
   <sheets>
     <sheet name="1er Parcial" sheetId="1" r:id="rId1"/>
     <sheet name="2o Parcial" sheetId="2" r:id="rId2"/>
-    <sheet name="3er Parcial" sheetId="3" r:id="rId3"/>
+    <sheet name="Final" sheetId="3" r:id="rId3"/>
   </sheets>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -106,6 +106,10 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <numFmts count="2">
+    <numFmt numFmtId="164" formatCode="0.0%"/>
+    <numFmt numFmtId="165" formatCode="0.0"/>
+  </numFmts>
   <fonts count="2">
     <font>
       <sz val="11"/>
@@ -158,8 +162,10 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
@@ -460,42 +466,45 @@
   <dimension ref="A1:K16"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" width="50.7109375" customWidth="1"/>
-    <col min="3" max="3" width="50.7109375" customWidth="1"/>
+    <col min="1" max="1" width="30.7109375" customWidth="1"/>
+    <col min="3" max="3" width="30.7109375" customWidth="1"/>
+    <col min="7" max="8" width="9.140625" style="1"/>
+    <col min="9" max="9" width="9.140625" style="2"/>
+    <col min="11" max="11" width="9.140625" style="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:11">
-      <c r="A1" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="1" t="s">
+      <c r="A1" s="3" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="3" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="1" t="s">
+      <c r="C1" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="1" t="s">
+      <c r="D1" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="1" t="s">
+      <c r="E1" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="1" t="s">
+      <c r="F1" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="1" t="s">
+      <c r="G1" s="3" t="s">
         <v>6</v>
       </c>
-      <c r="H1" s="1" t="s">
+      <c r="H1" s="3" t="s">
         <v>7</v>
       </c>
-      <c r="I1" s="1" t="s">
+      <c r="I1" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="J1" s="1" t="s">
+      <c r="J1" s="3" t="s">
         <v>9</v>
       </c>
-      <c r="K1" s="1" t="s">
+      <c r="K1" s="3" t="s">
         <v>10</v>
       </c>
     </row>
@@ -518,19 +527,19 @@
       <c r="F2">
         <v>0</v>
       </c>
-      <c r="G2">
-        <v>100</v>
-      </c>
-      <c r="H2">
-        <v>0</v>
-      </c>
-      <c r="I2">
+      <c r="G2" s="1">
+        <v>100</v>
+      </c>
+      <c r="H2" s="1">
+        <v>0</v>
+      </c>
+      <c r="I2" s="2">
         <v>9.1</v>
       </c>
       <c r="J2">
         <v>0</v>
       </c>
-      <c r="K2">
+      <c r="K2" s="1">
         <v>0</v>
       </c>
     </row>
@@ -553,19 +562,19 @@
       <c r="F3">
         <v>0</v>
       </c>
-      <c r="G3">
-        <v>100</v>
-      </c>
-      <c r="H3">
-        <v>0</v>
-      </c>
-      <c r="I3">
+      <c r="G3" s="1">
+        <v>100</v>
+      </c>
+      <c r="H3" s="1">
+        <v>0</v>
+      </c>
+      <c r="I3" s="2">
         <v>9.1</v>
       </c>
       <c r="J3">
         <v>0</v>
       </c>
-      <c r="K3">
+      <c r="K3" s="1">
         <v>0</v>
       </c>
     </row>
@@ -588,19 +597,19 @@
       <c r="F4">
         <v>0</v>
       </c>
-      <c r="G4">
-        <v>100</v>
-      </c>
-      <c r="H4">
-        <v>0</v>
-      </c>
-      <c r="I4">
+      <c r="G4" s="1">
+        <v>100</v>
+      </c>
+      <c r="H4" s="1">
+        <v>0</v>
+      </c>
+      <c r="I4" s="2">
         <v>9.199999999999999</v>
       </c>
       <c r="J4">
         <v>0</v>
       </c>
-      <c r="K4">
+      <c r="K4" s="1">
         <v>0</v>
       </c>
     </row>
@@ -623,19 +632,19 @@
       <c r="F5">
         <v>0</v>
       </c>
-      <c r="G5">
-        <v>100</v>
-      </c>
-      <c r="H5">
-        <v>0</v>
-      </c>
-      <c r="I5">
+      <c r="G5" s="1">
+        <v>100</v>
+      </c>
+      <c r="H5" s="1">
+        <v>0</v>
+      </c>
+      <c r="I5" s="2">
         <v>9.199999999999999</v>
       </c>
       <c r="J5">
         <v>0</v>
       </c>
-      <c r="K5">
+      <c r="K5" s="1">
         <v>0</v>
       </c>
     </row>
@@ -658,19 +667,19 @@
       <c r="F6">
         <v>0</v>
       </c>
-      <c r="G6">
-        <v>100</v>
-      </c>
-      <c r="H6">
-        <v>0</v>
-      </c>
-      <c r="I6">
+      <c r="G6" s="1">
+        <v>100</v>
+      </c>
+      <c r="H6" s="1">
+        <v>0</v>
+      </c>
+      <c r="I6" s="2">
         <v>9</v>
       </c>
       <c r="J6">
         <v>0</v>
       </c>
-      <c r="K6">
+      <c r="K6" s="1">
         <v>0</v>
       </c>
     </row>
@@ -693,19 +702,19 @@
       <c r="F7">
         <v>5</v>
       </c>
-      <c r="G7">
+      <c r="G7" s="1">
         <v>78.26000000000001</v>
       </c>
-      <c r="H7">
+      <c r="H7" s="1">
         <v>21.74</v>
       </c>
-      <c r="I7">
+      <c r="I7" s="2">
         <v>8.699999999999999</v>
       </c>
       <c r="J7">
         <v>5</v>
       </c>
-      <c r="K7">
+      <c r="K7" s="1">
         <v>21.74</v>
       </c>
     </row>
@@ -728,19 +737,19 @@
       <c r="F8">
         <v>5</v>
       </c>
-      <c r="G8">
+      <c r="G8" s="1">
         <v>78.26000000000001</v>
       </c>
-      <c r="H8">
+      <c r="H8" s="1">
         <v>21.74</v>
       </c>
-      <c r="I8">
+      <c r="I8" s="2">
         <v>8.4</v>
       </c>
       <c r="J8">
         <v>5</v>
       </c>
-      <c r="K8">
+      <c r="K8" s="1">
         <v>21.74</v>
       </c>
     </row>
@@ -763,19 +772,19 @@
       <c r="F9">
         <v>4</v>
       </c>
-      <c r="G9">
+      <c r="G9" s="1">
         <v>87.5</v>
       </c>
-      <c r="H9">
+      <c r="H9" s="1">
         <v>12.5</v>
       </c>
-      <c r="I9">
+      <c r="I9" s="2">
         <v>7.7</v>
       </c>
       <c r="J9">
         <v>0</v>
       </c>
-      <c r="K9">
+      <c r="K9" s="1">
         <v>0</v>
       </c>
     </row>
@@ -798,19 +807,19 @@
       <c r="F10">
         <v>6</v>
       </c>
-      <c r="G10">
+      <c r="G10" s="1">
         <v>84.20999999999999</v>
       </c>
-      <c r="H10">
+      <c r="H10" s="1">
         <v>15.79</v>
       </c>
-      <c r="I10">
+      <c r="I10" s="2">
         <v>7.8</v>
       </c>
       <c r="J10">
         <v>0</v>
       </c>
-      <c r="K10">
+      <c r="K10" s="1">
         <v>0</v>
       </c>
     </row>
@@ -833,19 +842,19 @@
       <c r="F11">
         <v>7</v>
       </c>
-      <c r="G11">
+      <c r="G11" s="1">
         <v>78.13</v>
       </c>
-      <c r="H11">
+      <c r="H11" s="1">
         <v>21.88</v>
       </c>
-      <c r="I11">
+      <c r="I11" s="2">
         <v>7.1</v>
       </c>
       <c r="J11">
         <v>0</v>
       </c>
-      <c r="K11">
+      <c r="K11" s="1">
         <v>0</v>
       </c>
     </row>
@@ -868,19 +877,19 @@
       <c r="F12">
         <v>14</v>
       </c>
-      <c r="G12">
+      <c r="G12" s="1">
         <v>57.58</v>
       </c>
-      <c r="H12">
+      <c r="H12" s="1">
         <v>42.42</v>
       </c>
-      <c r="I12">
+      <c r="I12" s="2">
         <v>7.4</v>
       </c>
       <c r="J12">
         <v>14</v>
       </c>
-      <c r="K12">
+      <c r="K12" s="1">
         <v>42.42</v>
       </c>
     </row>
@@ -903,19 +912,19 @@
       <c r="F13">
         <v>18</v>
       </c>
-      <c r="G13">
+      <c r="G13" s="1">
         <v>50</v>
       </c>
-      <c r="H13">
+      <c r="H13" s="1">
         <v>50</v>
       </c>
-      <c r="I13">
+      <c r="I13" s="2">
         <v>6.7</v>
       </c>
       <c r="J13">
         <v>1</v>
       </c>
-      <c r="K13">
+      <c r="K13" s="1">
         <v>2.78</v>
       </c>
     </row>
@@ -938,19 +947,19 @@
       <c r="F14">
         <v>18</v>
       </c>
-      <c r="G14">
+      <c r="G14" s="1">
         <v>50</v>
       </c>
-      <c r="H14">
+      <c r="H14" s="1">
         <v>50</v>
       </c>
-      <c r="I14">
+      <c r="I14" s="2">
         <v>6.7</v>
       </c>
       <c r="J14">
         <v>1</v>
       </c>
-      <c r="K14">
+      <c r="K14" s="1">
         <v>2.78</v>
       </c>
     </row>
@@ -973,19 +982,19 @@
       <c r="F15">
         <v>11</v>
       </c>
-      <c r="G15">
+      <c r="G15" s="1">
         <v>66.67</v>
       </c>
-      <c r="H15">
+      <c r="H15" s="1">
         <v>33.33</v>
       </c>
-      <c r="I15">
+      <c r="I15" s="2">
         <v>7.2</v>
       </c>
       <c r="J15">
         <v>0</v>
       </c>
-      <c r="K15">
+      <c r="K15" s="1">
         <v>0</v>
       </c>
     </row>
@@ -1008,19 +1017,19 @@
       <c r="F16">
         <v>4</v>
       </c>
-      <c r="G16">
+      <c r="G16" s="1">
         <v>82.61</v>
       </c>
-      <c r="H16">
+      <c r="H16" s="1">
         <v>17.39</v>
       </c>
-      <c r="I16">
+      <c r="I16" s="2">
         <v>7.4</v>
       </c>
       <c r="J16">
         <v>0</v>
       </c>
-      <c r="K16">
+      <c r="K16" s="1">
         <v>0</v>
       </c>
     </row>
@@ -1034,42 +1043,45 @@
   <dimension ref="A1:K16"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" width="50.7109375" customWidth="1"/>
-    <col min="3" max="3" width="50.7109375" customWidth="1"/>
+    <col min="1" max="1" width="30.7109375" customWidth="1"/>
+    <col min="3" max="3" width="30.7109375" customWidth="1"/>
+    <col min="7" max="8" width="9.140625" style="1"/>
+    <col min="9" max="9" width="9.140625" style="2"/>
+    <col min="11" max="11" width="9.140625" style="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:11">
-      <c r="A1" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="1" t="s">
+      <c r="A1" s="3" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="3" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="1" t="s">
+      <c r="C1" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="1" t="s">
+      <c r="D1" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="1" t="s">
+      <c r="E1" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="1" t="s">
+      <c r="F1" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="1" t="s">
+      <c r="G1" s="3" t="s">
         <v>6</v>
       </c>
-      <c r="H1" s="1" t="s">
+      <c r="H1" s="3" t="s">
         <v>7</v>
       </c>
-      <c r="I1" s="1" t="s">
+      <c r="I1" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="J1" s="1" t="s">
+      <c r="J1" s="3" t="s">
         <v>9</v>
       </c>
-      <c r="K1" s="1" t="s">
+      <c r="K1" s="3" t="s">
         <v>10</v>
       </c>
     </row>
@@ -1092,19 +1104,19 @@
       <c r="F2">
         <v>0</v>
       </c>
-      <c r="G2">
-        <v>100</v>
-      </c>
-      <c r="H2">
-        <v>0</v>
-      </c>
-      <c r="I2">
+      <c r="G2" s="1">
+        <v>100</v>
+      </c>
+      <c r="H2" s="1">
+        <v>0</v>
+      </c>
+      <c r="I2" s="2">
         <v>9.1</v>
       </c>
       <c r="J2">
         <v>0</v>
       </c>
-      <c r="K2">
+      <c r="K2" s="1">
         <v>0</v>
       </c>
     </row>
@@ -1127,19 +1139,19 @@
       <c r="F3">
         <v>0</v>
       </c>
-      <c r="G3">
-        <v>100</v>
-      </c>
-      <c r="H3">
-        <v>0</v>
-      </c>
-      <c r="I3">
+      <c r="G3" s="1">
+        <v>100</v>
+      </c>
+      <c r="H3" s="1">
+        <v>0</v>
+      </c>
+      <c r="I3" s="2">
         <v>9.1</v>
       </c>
       <c r="J3">
         <v>0</v>
       </c>
-      <c r="K3">
+      <c r="K3" s="1">
         <v>0</v>
       </c>
     </row>
@@ -1162,19 +1174,19 @@
       <c r="F4">
         <v>0</v>
       </c>
-      <c r="G4">
-        <v>100</v>
-      </c>
-      <c r="H4">
-        <v>0</v>
-      </c>
-      <c r="I4">
+      <c r="G4" s="1">
+        <v>100</v>
+      </c>
+      <c r="H4" s="1">
+        <v>0</v>
+      </c>
+      <c r="I4" s="2">
         <v>9.199999999999999</v>
       </c>
       <c r="J4">
         <v>0</v>
       </c>
-      <c r="K4">
+      <c r="K4" s="1">
         <v>0</v>
       </c>
     </row>
@@ -1197,19 +1209,19 @@
       <c r="F5">
         <v>0</v>
       </c>
-      <c r="G5">
-        <v>100</v>
-      </c>
-      <c r="H5">
-        <v>0</v>
-      </c>
-      <c r="I5">
+      <c r="G5" s="1">
+        <v>100</v>
+      </c>
+      <c r="H5" s="1">
+        <v>0</v>
+      </c>
+      <c r="I5" s="2">
         <v>9</v>
       </c>
       <c r="J5">
         <v>0</v>
       </c>
-      <c r="K5">
+      <c r="K5" s="1">
         <v>0</v>
       </c>
     </row>
@@ -1232,19 +1244,19 @@
       <c r="F6">
         <v>0</v>
       </c>
-      <c r="G6">
-        <v>100</v>
-      </c>
-      <c r="H6">
-        <v>0</v>
-      </c>
-      <c r="I6">
+      <c r="G6" s="1">
+        <v>100</v>
+      </c>
+      <c r="H6" s="1">
+        <v>0</v>
+      </c>
+      <c r="I6" s="2">
         <v>9</v>
       </c>
       <c r="J6">
         <v>0</v>
       </c>
-      <c r="K6">
+      <c r="K6" s="1">
         <v>0</v>
       </c>
     </row>
@@ -1267,16 +1279,16 @@
       <c r="F7">
         <v>23</v>
       </c>
-      <c r="G7">
-        <v>0</v>
-      </c>
-      <c r="H7">
+      <c r="G7" s="1">
+        <v>0</v>
+      </c>
+      <c r="H7" s="1">
         <v>100</v>
       </c>
       <c r="J7">
         <v>23</v>
       </c>
-      <c r="K7">
+      <c r="K7" s="1">
         <v>100</v>
       </c>
     </row>
@@ -1299,16 +1311,16 @@
       <c r="F8">
         <v>23</v>
       </c>
-      <c r="G8">
-        <v>0</v>
-      </c>
-      <c r="H8">
+      <c r="G8" s="1">
+        <v>0</v>
+      </c>
+      <c r="H8" s="1">
         <v>100</v>
       </c>
       <c r="J8">
         <v>23</v>
       </c>
-      <c r="K8">
+      <c r="K8" s="1">
         <v>100</v>
       </c>
     </row>
@@ -1331,19 +1343,19 @@
       <c r="F9">
         <v>5</v>
       </c>
-      <c r="G9">
+      <c r="G9" s="1">
         <v>84.38</v>
       </c>
-      <c r="H9">
+      <c r="H9" s="1">
         <v>15.63</v>
       </c>
-      <c r="I9">
+      <c r="I9" s="2">
         <v>7.5</v>
       </c>
       <c r="J9">
         <v>0</v>
       </c>
-      <c r="K9">
+      <c r="K9" s="1">
         <v>0</v>
       </c>
     </row>
@@ -1366,19 +1378,19 @@
       <c r="F10">
         <v>7</v>
       </c>
-      <c r="G10">
+      <c r="G10" s="1">
         <v>81.58</v>
       </c>
-      <c r="H10">
+      <c r="H10" s="1">
         <v>18.42</v>
       </c>
-      <c r="I10">
+      <c r="I10" s="2">
         <v>7.5</v>
       </c>
       <c r="J10">
         <v>0</v>
       </c>
-      <c r="K10">
+      <c r="K10" s="1">
         <v>0</v>
       </c>
     </row>
@@ -1401,19 +1413,19 @@
       <c r="F11">
         <v>7</v>
       </c>
-      <c r="G11">
+      <c r="G11" s="1">
         <v>78.13</v>
       </c>
-      <c r="H11">
+      <c r="H11" s="1">
         <v>21.88</v>
       </c>
-      <c r="I11">
+      <c r="I11" s="2">
         <v>6.8</v>
       </c>
       <c r="J11">
         <v>0</v>
       </c>
-      <c r="K11">
+      <c r="K11" s="1">
         <v>0</v>
       </c>
     </row>
@@ -1436,16 +1448,16 @@
       <c r="F12">
         <v>33</v>
       </c>
-      <c r="G12">
-        <v>0</v>
-      </c>
-      <c r="H12">
+      <c r="G12" s="1">
+        <v>0</v>
+      </c>
+      <c r="H12" s="1">
         <v>100</v>
       </c>
       <c r="J12">
         <v>33</v>
       </c>
-      <c r="K12">
+      <c r="K12" s="1">
         <v>100</v>
       </c>
     </row>
@@ -1468,16 +1480,16 @@
       <c r="F13">
         <v>36</v>
       </c>
-      <c r="G13">
-        <v>0</v>
-      </c>
-      <c r="H13">
+      <c r="G13" s="1">
+        <v>0</v>
+      </c>
+      <c r="H13" s="1">
         <v>100</v>
       </c>
       <c r="J13">
         <v>36</v>
       </c>
-      <c r="K13">
+      <c r="K13" s="1">
         <v>100</v>
       </c>
     </row>
@@ -1500,16 +1512,16 @@
       <c r="F14">
         <v>36</v>
       </c>
-      <c r="G14">
-        <v>0</v>
-      </c>
-      <c r="H14">
+      <c r="G14" s="1">
+        <v>0</v>
+      </c>
+      <c r="H14" s="1">
         <v>100</v>
       </c>
       <c r="J14">
         <v>36</v>
       </c>
-      <c r="K14">
+      <c r="K14" s="1">
         <v>100</v>
       </c>
     </row>
@@ -1532,19 +1544,19 @@
       <c r="F15">
         <v>21</v>
       </c>
-      <c r="G15">
+      <c r="G15" s="1">
         <v>36.36</v>
       </c>
-      <c r="H15">
+      <c r="H15" s="1">
         <v>63.64</v>
       </c>
-      <c r="I15">
+      <c r="I15" s="2">
         <v>9</v>
       </c>
       <c r="J15">
         <v>21</v>
       </c>
-      <c r="K15">
+      <c r="K15" s="1">
         <v>63.64</v>
       </c>
     </row>
@@ -1567,19 +1579,19 @@
       <c r="F16">
         <v>11</v>
       </c>
-      <c r="G16">
+      <c r="G16" s="1">
         <v>52.17</v>
       </c>
-      <c r="H16">
+      <c r="H16" s="1">
         <v>47.83</v>
       </c>
-      <c r="I16">
+      <c r="I16" s="2">
         <v>9.300000000000001</v>
       </c>
       <c r="J16">
         <v>11</v>
       </c>
-      <c r="K16">
+      <c r="K16" s="1">
         <v>47.83</v>
       </c>
     </row>
@@ -1593,42 +1605,45 @@
   <dimension ref="A1:K16"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" width="50.7109375" customWidth="1"/>
-    <col min="3" max="3" width="50.7109375" customWidth="1"/>
+    <col min="1" max="1" width="30.7109375" customWidth="1"/>
+    <col min="3" max="3" width="30.7109375" customWidth="1"/>
+    <col min="7" max="8" width="9.140625" style="1"/>
+    <col min="9" max="9" width="9.140625" style="2"/>
+    <col min="11" max="11" width="9.140625" style="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:11">
-      <c r="A1" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="1" t="s">
+      <c r="A1" s="3" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="3" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="1" t="s">
+      <c r="C1" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="1" t="s">
+      <c r="D1" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="1" t="s">
+      <c r="E1" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="1" t="s">
+      <c r="F1" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="1" t="s">
+      <c r="G1" s="3" t="s">
         <v>6</v>
       </c>
-      <c r="H1" s="1" t="s">
+      <c r="H1" s="3" t="s">
         <v>7</v>
       </c>
-      <c r="I1" s="1" t="s">
+      <c r="I1" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="J1" s="1" t="s">
+      <c r="J1" s="3" t="s">
         <v>9</v>
       </c>
-      <c r="K1" s="1" t="s">
+      <c r="K1" s="3" t="s">
         <v>10</v>
       </c>
     </row>
@@ -1651,19 +1666,19 @@
       <c r="F2">
         <v>0</v>
       </c>
-      <c r="G2">
-        <v>100</v>
-      </c>
-      <c r="H2">
-        <v>0</v>
-      </c>
-      <c r="I2">
+      <c r="G2" s="1">
+        <v>100</v>
+      </c>
+      <c r="H2" s="1">
+        <v>0</v>
+      </c>
+      <c r="I2" s="2">
         <v>9.199999999999999</v>
       </c>
       <c r="J2">
         <v>0</v>
       </c>
-      <c r="K2">
+      <c r="K2" s="1">
         <v>0</v>
       </c>
     </row>
@@ -1686,19 +1701,19 @@
       <c r="F3">
         <v>0</v>
       </c>
-      <c r="G3">
-        <v>100</v>
-      </c>
-      <c r="H3">
-        <v>0</v>
-      </c>
-      <c r="I3">
+      <c r="G3" s="1">
+        <v>100</v>
+      </c>
+      <c r="H3" s="1">
+        <v>0</v>
+      </c>
+      <c r="I3" s="2">
         <v>9.1</v>
       </c>
       <c r="J3">
         <v>0</v>
       </c>
-      <c r="K3">
+      <c r="K3" s="1">
         <v>0</v>
       </c>
     </row>
@@ -1721,19 +1736,19 @@
       <c r="F4">
         <v>0</v>
       </c>
-      <c r="G4">
-        <v>100</v>
-      </c>
-      <c r="H4">
-        <v>0</v>
-      </c>
-      <c r="I4">
+      <c r="G4" s="1">
+        <v>100</v>
+      </c>
+      <c r="H4" s="1">
+        <v>0</v>
+      </c>
+      <c r="I4" s="2">
         <v>9.199999999999999</v>
       </c>
       <c r="J4">
         <v>0</v>
       </c>
-      <c r="K4">
+      <c r="K4" s="1">
         <v>0</v>
       </c>
     </row>
@@ -1756,19 +1771,19 @@
       <c r="F5">
         <v>0</v>
       </c>
-      <c r="G5">
-        <v>100</v>
-      </c>
-      <c r="H5">
-        <v>0</v>
-      </c>
-      <c r="I5">
+      <c r="G5" s="1">
+        <v>100</v>
+      </c>
+      <c r="H5" s="1">
+        <v>0</v>
+      </c>
+      <c r="I5" s="2">
         <v>9.1</v>
       </c>
       <c r="J5">
         <v>0</v>
       </c>
-      <c r="K5">
+      <c r="K5" s="1">
         <v>0</v>
       </c>
     </row>
@@ -1791,19 +1806,19 @@
       <c r="F6">
         <v>0</v>
       </c>
-      <c r="G6">
-        <v>100</v>
-      </c>
-      <c r="H6">
-        <v>0</v>
-      </c>
-      <c r="I6">
+      <c r="G6" s="1">
+        <v>100</v>
+      </c>
+      <c r="H6" s="1">
+        <v>0</v>
+      </c>
+      <c r="I6" s="2">
         <v>9</v>
       </c>
       <c r="J6">
         <v>0</v>
       </c>
-      <c r="K6">
+      <c r="K6" s="1">
         <v>0</v>
       </c>
     </row>
@@ -1826,19 +1841,19 @@
       <c r="F7">
         <v>5</v>
       </c>
-      <c r="G7">
+      <c r="G7" s="1">
         <v>78.26000000000001</v>
       </c>
-      <c r="H7">
+      <c r="H7" s="1">
         <v>21.74</v>
       </c>
-      <c r="I7">
+      <c r="I7" s="2">
         <v>8.699999999999999</v>
       </c>
       <c r="J7">
         <v>5</v>
       </c>
-      <c r="K7">
+      <c r="K7" s="1">
         <v>21.74</v>
       </c>
     </row>
@@ -1861,19 +1876,19 @@
       <c r="F8">
         <v>5</v>
       </c>
-      <c r="G8">
+      <c r="G8" s="1">
         <v>78.26000000000001</v>
       </c>
-      <c r="H8">
+      <c r="H8" s="1">
         <v>21.74</v>
       </c>
-      <c r="I8">
+      <c r="I8" s="2">
         <v>8.4</v>
       </c>
       <c r="J8">
         <v>5</v>
       </c>
-      <c r="K8">
+      <c r="K8" s="1">
         <v>21.74</v>
       </c>
     </row>
@@ -1896,19 +1911,19 @@
       <c r="F9">
         <v>5</v>
       </c>
-      <c r="G9">
+      <c r="G9" s="1">
         <v>84.38</v>
       </c>
-      <c r="H9">
+      <c r="H9" s="1">
         <v>15.63</v>
       </c>
-      <c r="I9">
+      <c r="I9" s="2">
         <v>7.7</v>
       </c>
       <c r="J9">
         <v>0</v>
       </c>
-      <c r="K9">
+      <c r="K9" s="1">
         <v>0</v>
       </c>
     </row>
@@ -1931,19 +1946,19 @@
       <c r="F10">
         <v>7</v>
       </c>
-      <c r="G10">
+      <c r="G10" s="1">
         <v>81.58</v>
       </c>
-      <c r="H10">
+      <c r="H10" s="1">
         <v>18.42</v>
       </c>
-      <c r="I10">
+      <c r="I10" s="2">
         <v>7.7</v>
       </c>
       <c r="J10">
         <v>0</v>
       </c>
-      <c r="K10">
+      <c r="K10" s="1">
         <v>0</v>
       </c>
     </row>
@@ -1966,19 +1981,19 @@
       <c r="F11">
         <v>7</v>
       </c>
-      <c r="G11">
+      <c r="G11" s="1">
         <v>78.13</v>
       </c>
-      <c r="H11">
+      <c r="H11" s="1">
         <v>21.88</v>
       </c>
-      <c r="I11">
+      <c r="I11" s="2">
         <v>7.1</v>
       </c>
       <c r="J11">
         <v>0</v>
       </c>
-      <c r="K11">
+      <c r="K11" s="1">
         <v>0</v>
       </c>
     </row>
@@ -2001,19 +2016,19 @@
       <c r="F12">
         <v>14</v>
       </c>
-      <c r="G12">
+      <c r="G12" s="1">
         <v>57.58</v>
       </c>
-      <c r="H12">
+      <c r="H12" s="1">
         <v>42.42</v>
       </c>
-      <c r="I12">
+      <c r="I12" s="2">
         <v>7.4</v>
       </c>
       <c r="J12">
         <v>14</v>
       </c>
-      <c r="K12">
+      <c r="K12" s="1">
         <v>42.42</v>
       </c>
     </row>
@@ -2036,19 +2051,19 @@
       <c r="F13">
         <v>18</v>
       </c>
-      <c r="G13">
+      <c r="G13" s="1">
         <v>50</v>
       </c>
-      <c r="H13">
+      <c r="H13" s="1">
         <v>50</v>
       </c>
-      <c r="I13">
+      <c r="I13" s="2">
         <v>6.7</v>
       </c>
       <c r="J13">
         <v>1</v>
       </c>
-      <c r="K13">
+      <c r="K13" s="1">
         <v>2.78</v>
       </c>
     </row>
@@ -2071,19 +2086,19 @@
       <c r="F14">
         <v>18</v>
       </c>
-      <c r="G14">
+      <c r="G14" s="1">
         <v>50</v>
       </c>
-      <c r="H14">
+      <c r="H14" s="1">
         <v>50</v>
       </c>
-      <c r="I14">
+      <c r="I14" s="2">
         <v>6.7</v>
       </c>
       <c r="J14">
         <v>1</v>
       </c>
-      <c r="K14">
+      <c r="K14" s="1">
         <v>2.78</v>
       </c>
     </row>
@@ -2106,19 +2121,19 @@
       <c r="F15">
         <v>9</v>
       </c>
-      <c r="G15">
+      <c r="G15" s="1">
         <v>72.73</v>
       </c>
-      <c r="H15">
+      <c r="H15" s="1">
         <v>27.27</v>
       </c>
-      <c r="I15">
+      <c r="I15" s="2">
         <v>7.5</v>
       </c>
       <c r="J15">
         <v>0</v>
       </c>
-      <c r="K15">
+      <c r="K15" s="1">
         <v>0</v>
       </c>
     </row>
@@ -2141,19 +2156,19 @@
       <c r="F16">
         <v>4</v>
       </c>
-      <c r="G16">
+      <c r="G16" s="1">
         <v>82.61</v>
       </c>
-      <c r="H16">
+      <c r="H16" s="1">
         <v>17.39</v>
       </c>
-      <c r="I16">
+      <c r="I16" s="2">
         <v>7.8</v>
       </c>
       <c r="J16">
         <v>0</v>
       </c>
-      <c r="K16">
+      <c r="K16" s="1">
         <v>0</v>
       </c>
     </row>

--- a/academias/Electricidad - Estadisticos 20211.xlsx
+++ b/academias/Electricidad - Estadisticos 20211.xlsx
@@ -107,7 +107,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="2">
-    <numFmt numFmtId="164" formatCode="0.0%"/>
+    <numFmt numFmtId="164" formatCode="0.0\%"/>
     <numFmt numFmtId="165" formatCode="0.0"/>
   </numFmts>
   <fonts count="2">

--- a/academias/Electricidad - Estadisticos 20211.xlsx
+++ b/academias/Electricidad - Estadisticos 20211.xlsx
@@ -697,25 +697,25 @@
         <v>23</v>
       </c>
       <c r="E7">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="F7">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="G7" s="1">
-        <v>78.26000000000001</v>
+        <v>86.95999999999999</v>
       </c>
       <c r="H7" s="1">
-        <v>21.74</v>
+        <v>13.04</v>
       </c>
       <c r="I7" s="2">
-        <v>8.699999999999999</v>
+        <v>8.5</v>
       </c>
       <c r="J7">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="K7" s="1">
-        <v>21.74</v>
+        <v>13.04</v>
       </c>
     </row>
     <row r="8" spans="1:11">
@@ -732,25 +732,25 @@
         <v>23</v>
       </c>
       <c r="E8">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="F8">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="G8" s="1">
-        <v>78.26000000000001</v>
+        <v>91.3</v>
       </c>
       <c r="H8" s="1">
-        <v>21.74</v>
+        <v>8.699999999999999</v>
       </c>
       <c r="I8" s="2">
-        <v>8.4</v>
+        <v>8.1</v>
       </c>
       <c r="J8">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="K8" s="1">
-        <v>21.74</v>
+        <v>8.699999999999999</v>
       </c>
     </row>
     <row r="9" spans="1:11">
@@ -872,25 +872,25 @@
         <v>33</v>
       </c>
       <c r="E12">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="F12">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="G12" s="1">
-        <v>57.58</v>
+        <v>66.67</v>
       </c>
       <c r="H12" s="1">
-        <v>42.42</v>
+        <v>33.33</v>
       </c>
       <c r="I12" s="2">
-        <v>7.4</v>
+        <v>6.5</v>
       </c>
       <c r="J12">
-        <v>14</v>
+        <v>0</v>
       </c>
       <c r="K12" s="1">
-        <v>42.42</v>
+        <v>0</v>
       </c>
     </row>
     <row r="13" spans="1:11">
@@ -1274,22 +1274,25 @@
         <v>23</v>
       </c>
       <c r="E7">
-        <v>0</v>
+        <v>18</v>
       </c>
       <c r="F7">
-        <v>23</v>
+        <v>5</v>
       </c>
       <c r="G7" s="1">
-        <v>0</v>
+        <v>78.26000000000001</v>
       </c>
       <c r="H7" s="1">
-        <v>100</v>
+        <v>21.74</v>
+      </c>
+      <c r="I7" s="2">
+        <v>9.199999999999999</v>
       </c>
       <c r="J7">
-        <v>23</v>
+        <v>5</v>
       </c>
       <c r="K7" s="1">
-        <v>100</v>
+        <v>21.74</v>
       </c>
     </row>
     <row r="8" spans="1:11">
@@ -1306,22 +1309,25 @@
         <v>23</v>
       </c>
       <c r="E8">
-        <v>0</v>
+        <v>16</v>
       </c>
       <c r="F8">
-        <v>23</v>
+        <v>7</v>
       </c>
       <c r="G8" s="1">
-        <v>0</v>
+        <v>69.56999999999999</v>
       </c>
       <c r="H8" s="1">
-        <v>100</v>
+        <v>30.43</v>
+      </c>
+      <c r="I8" s="2">
+        <v>8.5</v>
       </c>
       <c r="J8">
-        <v>23</v>
+        <v>7</v>
       </c>
       <c r="K8" s="1">
-        <v>100</v>
+        <v>30.43</v>
       </c>
     </row>
     <row r="9" spans="1:11">
@@ -1443,22 +1449,25 @@
         <v>33</v>
       </c>
       <c r="E12">
-        <v>0</v>
+        <v>19</v>
       </c>
       <c r="F12">
-        <v>33</v>
+        <v>14</v>
       </c>
       <c r="G12" s="1">
-        <v>0</v>
+        <v>57.58</v>
       </c>
       <c r="H12" s="1">
-        <v>100</v>
+        <v>42.42</v>
+      </c>
+      <c r="I12" s="2">
+        <v>6.3</v>
       </c>
       <c r="J12">
-        <v>33</v>
+        <v>11</v>
       </c>
       <c r="K12" s="1">
-        <v>100</v>
+        <v>33.33</v>
       </c>
     </row>
     <row r="13" spans="1:11">
@@ -1836,25 +1845,25 @@
         <v>23</v>
       </c>
       <c r="E7">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="F7">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="G7" s="1">
-        <v>78.26000000000001</v>
+        <v>86.95999999999999</v>
       </c>
       <c r="H7" s="1">
-        <v>21.74</v>
+        <v>13.04</v>
       </c>
       <c r="I7" s="2">
-        <v>8.699999999999999</v>
+        <v>9.1</v>
       </c>
       <c r="J7">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="K7" s="1">
-        <v>21.74</v>
+        <v>13.04</v>
       </c>
     </row>
     <row r="8" spans="1:11">
@@ -1871,25 +1880,25 @@
         <v>23</v>
       </c>
       <c r="E8">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="F8">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="G8" s="1">
-        <v>78.26000000000001</v>
+        <v>91.3</v>
       </c>
       <c r="H8" s="1">
-        <v>21.74</v>
+        <v>8.699999999999999</v>
       </c>
       <c r="I8" s="2">
-        <v>8.4</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="J8">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="K8" s="1">
-        <v>21.74</v>
+        <v>8.699999999999999</v>
       </c>
     </row>
     <row r="9" spans="1:11">
@@ -2023,13 +2032,13 @@
         <v>42.42</v>
       </c>
       <c r="I12" s="2">
-        <v>7.4</v>
+        <v>6.3</v>
       </c>
       <c r="J12">
-        <v>14</v>
+        <v>0</v>
       </c>
       <c r="K12" s="1">
-        <v>42.42</v>
+        <v>0</v>
       </c>
     </row>
     <row r="13" spans="1:11">

--- a/academias/Electricidad - Estadisticos 20211.xlsx
+++ b/academias/Electricidad - Estadisticos 20211.xlsx
@@ -922,10 +922,10 @@
         <v>6.7</v>
       </c>
       <c r="J13">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K13" s="1">
-        <v>2.78</v>
+        <v>0</v>
       </c>
     </row>
     <row r="14" spans="1:11">
@@ -957,10 +957,10 @@
         <v>6.7</v>
       </c>
       <c r="J14">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K14" s="1">
-        <v>2.78</v>
+        <v>0</v>
       </c>
     </row>
     <row r="15" spans="1:11">
@@ -1484,22 +1484,25 @@
         <v>36</v>
       </c>
       <c r="E13">
-        <v>0</v>
+        <v>36</v>
       </c>
       <c r="F13">
-        <v>36</v>
+        <v>0</v>
       </c>
       <c r="G13" s="1">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="H13" s="1">
-        <v>100</v>
+        <v>0</v>
+      </c>
+      <c r="I13" s="2">
+        <v>9.1</v>
       </c>
       <c r="J13">
-        <v>36</v>
+        <v>0</v>
       </c>
       <c r="K13" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="14" spans="1:11">
@@ -1516,22 +1519,25 @@
         <v>36</v>
       </c>
       <c r="E14">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="F14">
-        <v>36</v>
+        <v>11</v>
       </c>
       <c r="G14" s="1">
-        <v>0</v>
+        <v>69.44</v>
       </c>
       <c r="H14" s="1">
-        <v>100</v>
+        <v>30.56</v>
+      </c>
+      <c r="I14" s="2">
+        <v>7.8</v>
       </c>
       <c r="J14">
-        <v>36</v>
+        <v>0</v>
       </c>
       <c r="K14" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="15" spans="1:11">
@@ -2055,25 +2061,25 @@
         <v>36</v>
       </c>
       <c r="E13">
-        <v>18</v>
+        <v>36</v>
       </c>
       <c r="F13">
-        <v>18</v>
+        <v>0</v>
       </c>
       <c r="G13" s="1">
-        <v>50</v>
+        <v>100</v>
       </c>
       <c r="H13" s="1">
-        <v>50</v>
+        <v>0</v>
       </c>
       <c r="I13" s="2">
-        <v>6.7</v>
+        <v>8.1</v>
       </c>
       <c r="J13">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K13" s="1">
-        <v>2.78</v>
+        <v>0</v>
       </c>
     </row>
     <row r="14" spans="1:11">
@@ -2090,25 +2096,25 @@
         <v>36</v>
       </c>
       <c r="E14">
-        <v>18</v>
+        <v>25</v>
       </c>
       <c r="F14">
-        <v>18</v>
+        <v>11</v>
       </c>
       <c r="G14" s="1">
-        <v>50</v>
+        <v>69.44</v>
       </c>
       <c r="H14" s="1">
-        <v>50</v>
+        <v>30.56</v>
       </c>
       <c r="I14" s="2">
-        <v>6.7</v>
+        <v>7.3</v>
       </c>
       <c r="J14">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K14" s="1">
-        <v>2.78</v>
+        <v>0</v>
       </c>
     </row>
     <row r="15" spans="1:11">

--- a/academias/Electricidad - Estadisticos 20211.xlsx
+++ b/academias/Electricidad - Estadisticos 20211.xlsx
@@ -697,25 +697,25 @@
         <v>23</v>
       </c>
       <c r="E7">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="F7">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="G7" s="1">
-        <v>86.95999999999999</v>
+        <v>100</v>
       </c>
       <c r="H7" s="1">
-        <v>13.04</v>
+        <v>0</v>
       </c>
       <c r="I7" s="2">
-        <v>8.5</v>
+        <v>8.1</v>
       </c>
       <c r="J7">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="K7" s="1">
-        <v>13.04</v>
+        <v>0</v>
       </c>
     </row>
     <row r="8" spans="1:11">
@@ -732,25 +732,25 @@
         <v>23</v>
       </c>
       <c r="E8">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="F8">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="G8" s="1">
-        <v>91.3</v>
+        <v>100</v>
       </c>
       <c r="H8" s="1">
-        <v>8.699999999999999</v>
+        <v>0</v>
       </c>
       <c r="I8" s="2">
-        <v>8.1</v>
+        <v>7.9</v>
       </c>
       <c r="J8">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="K8" s="1">
-        <v>8.699999999999999</v>
+        <v>0</v>
       </c>
     </row>
     <row r="9" spans="1:11">
@@ -1274,25 +1274,25 @@
         <v>23</v>
       </c>
       <c r="E7">
-        <v>18</v>
+        <v>23</v>
       </c>
       <c r="F7">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="G7" s="1">
-        <v>78.26000000000001</v>
+        <v>100</v>
       </c>
       <c r="H7" s="1">
-        <v>21.74</v>
+        <v>0</v>
       </c>
       <c r="I7" s="2">
-        <v>9.199999999999999</v>
+        <v>8.5</v>
       </c>
       <c r="J7">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="K7" s="1">
-        <v>21.74</v>
+        <v>0</v>
       </c>
     </row>
     <row r="8" spans="1:11">
@@ -1309,25 +1309,25 @@
         <v>23</v>
       </c>
       <c r="E8">
-        <v>16</v>
+        <v>23</v>
       </c>
       <c r="F8">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="G8" s="1">
-        <v>69.56999999999999</v>
+        <v>100</v>
       </c>
       <c r="H8" s="1">
-        <v>30.43</v>
+        <v>0</v>
       </c>
       <c r="I8" s="2">
-        <v>8.5</v>
+        <v>7.7</v>
       </c>
       <c r="J8">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="K8" s="1">
-        <v>30.43</v>
+        <v>0</v>
       </c>
     </row>
     <row r="9" spans="1:11">
@@ -1461,13 +1461,13 @@
         <v>42.42</v>
       </c>
       <c r="I12" s="2">
-        <v>6.3</v>
+        <v>6</v>
       </c>
       <c r="J12">
-        <v>11</v>
+        <v>0</v>
       </c>
       <c r="K12" s="1">
-        <v>33.33</v>
+        <v>0</v>
       </c>
     </row>
     <row r="13" spans="1:11">
@@ -1554,25 +1554,25 @@
         <v>33</v>
       </c>
       <c r="E15">
-        <v>12</v>
+        <v>25</v>
       </c>
       <c r="F15">
-        <v>21</v>
+        <v>8</v>
       </c>
       <c r="G15" s="1">
-        <v>36.36</v>
+        <v>75.76000000000001</v>
       </c>
       <c r="H15" s="1">
-        <v>63.64</v>
+        <v>24.24</v>
       </c>
       <c r="I15" s="2">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="J15">
-        <v>21</v>
+        <v>0</v>
       </c>
       <c r="K15" s="1">
-        <v>63.64</v>
+        <v>0</v>
       </c>
     </row>
     <row r="16" spans="1:11">
@@ -1589,25 +1589,25 @@
         <v>23</v>
       </c>
       <c r="E16">
-        <v>12</v>
+        <v>21</v>
       </c>
       <c r="F16">
-        <v>11</v>
+        <v>2</v>
       </c>
       <c r="G16" s="1">
-        <v>52.17</v>
+        <v>91.3</v>
       </c>
       <c r="H16" s="1">
-        <v>47.83</v>
+        <v>8.699999999999999</v>
       </c>
       <c r="I16" s="2">
-        <v>9.300000000000001</v>
+        <v>7.9</v>
       </c>
       <c r="J16">
-        <v>11</v>
+        <v>0</v>
       </c>
       <c r="K16" s="1">
-        <v>47.83</v>
+        <v>0</v>
       </c>
     </row>
   </sheetData>
@@ -1758,7 +1758,7 @@
         <v>0</v>
       </c>
       <c r="I4" s="2">
-        <v>9.199999999999999</v>
+        <v>9.1</v>
       </c>
       <c r="J4">
         <v>0</v>
@@ -1793,7 +1793,7 @@
         <v>0</v>
       </c>
       <c r="I5" s="2">
-        <v>9.1</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="J5">
         <v>0</v>
@@ -1828,7 +1828,7 @@
         <v>0</v>
       </c>
       <c r="I6" s="2">
-        <v>9</v>
+        <v>9.1</v>
       </c>
       <c r="J6">
         <v>0</v>
@@ -1851,25 +1851,25 @@
         <v>23</v>
       </c>
       <c r="E7">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="F7">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="G7" s="1">
-        <v>86.95999999999999</v>
+        <v>100</v>
       </c>
       <c r="H7" s="1">
-        <v>13.04</v>
+        <v>0</v>
       </c>
       <c r="I7" s="2">
-        <v>9.1</v>
+        <v>8.1</v>
       </c>
       <c r="J7">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="K7" s="1">
-        <v>13.04</v>
+        <v>0</v>
       </c>
     </row>
     <row r="8" spans="1:11">
@@ -1886,25 +1886,25 @@
         <v>23</v>
       </c>
       <c r="E8">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="F8">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="G8" s="1">
-        <v>91.3</v>
+        <v>100</v>
       </c>
       <c r="H8" s="1">
-        <v>8.699999999999999</v>
+        <v>0</v>
       </c>
       <c r="I8" s="2">
-        <v>8.199999999999999</v>
+        <v>7.5</v>
       </c>
       <c r="J8">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="K8" s="1">
-        <v>8.699999999999999</v>
+        <v>0</v>
       </c>
     </row>
     <row r="9" spans="1:11">
@@ -1921,19 +1921,19 @@
         <v>32</v>
       </c>
       <c r="E9">
-        <v>27</v>
+        <v>32</v>
       </c>
       <c r="F9">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="G9" s="1">
-        <v>84.38</v>
+        <v>100</v>
       </c>
       <c r="H9" s="1">
-        <v>15.63</v>
+        <v>0</v>
       </c>
       <c r="I9" s="2">
-        <v>7.7</v>
+        <v>7.8</v>
       </c>
       <c r="J9">
         <v>0</v>
@@ -1956,16 +1956,16 @@
         <v>38</v>
       </c>
       <c r="E10">
-        <v>31</v>
+        <v>36</v>
       </c>
       <c r="F10">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="G10" s="1">
-        <v>81.58</v>
+        <v>94.73999999999999</v>
       </c>
       <c r="H10" s="1">
-        <v>18.42</v>
+        <v>5.26</v>
       </c>
       <c r="I10" s="2">
         <v>7.7</v>
@@ -1991,19 +1991,19 @@
         <v>32</v>
       </c>
       <c r="E11">
-        <v>25</v>
+        <v>32</v>
       </c>
       <c r="F11">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="G11" s="1">
-        <v>78.13</v>
+        <v>100</v>
       </c>
       <c r="H11" s="1">
-        <v>21.88</v>
+        <v>0</v>
       </c>
       <c r="I11" s="2">
-        <v>7.1</v>
+        <v>7.4</v>
       </c>
       <c r="J11">
         <v>0</v>
@@ -2026,19 +2026,19 @@
         <v>33</v>
       </c>
       <c r="E12">
-        <v>19</v>
+        <v>23</v>
       </c>
       <c r="F12">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="G12" s="1">
-        <v>57.58</v>
+        <v>69.7</v>
       </c>
       <c r="H12" s="1">
-        <v>42.42</v>
+        <v>30.3</v>
       </c>
       <c r="I12" s="2">
-        <v>6.3</v>
+        <v>6.1</v>
       </c>
       <c r="J12">
         <v>0</v>
@@ -2073,7 +2073,7 @@
         <v>0</v>
       </c>
       <c r="I13" s="2">
-        <v>8.1</v>
+        <v>8.300000000000001</v>
       </c>
       <c r="J13">
         <v>0</v>
@@ -2096,19 +2096,19 @@
         <v>36</v>
       </c>
       <c r="E14">
-        <v>25</v>
+        <v>29</v>
       </c>
       <c r="F14">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="G14" s="1">
-        <v>69.44</v>
+        <v>80.56</v>
       </c>
       <c r="H14" s="1">
-        <v>30.56</v>
+        <v>19.44</v>
       </c>
       <c r="I14" s="2">
-        <v>7.3</v>
+        <v>7.8</v>
       </c>
       <c r="J14">
         <v>0</v>
@@ -2143,7 +2143,7 @@
         <v>27.27</v>
       </c>
       <c r="I15" s="2">
-        <v>7.5</v>
+        <v>6.9</v>
       </c>
       <c r="J15">
         <v>0</v>
@@ -2166,19 +2166,19 @@
         <v>23</v>
       </c>
       <c r="E16">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="F16">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="G16" s="1">
-        <v>82.61</v>
+        <v>91.3</v>
       </c>
       <c r="H16" s="1">
-        <v>17.39</v>
+        <v>8.699999999999999</v>
       </c>
       <c r="I16" s="2">
-        <v>7.8</v>
+        <v>7.4</v>
       </c>
       <c r="J16">
         <v>0</v>
